--- a/api-keys.xlsx
+++ b/api-keys.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>b05449c580f85012517bb646171428a5</t>
   </si>
@@ -25,10 +25,10 @@
     <t>19ea79044fa1ac37de2e28f55eaa7ed2</t>
   </si>
   <si>
-    <t>188bc95a0194a1ad9a6ddf514f0ac11f</t>
-  </si>
-  <si>
-    <t>f8b9e9bf0c7576d6cc0fb08358f7fa23</t>
+    <t>a5c889290ed179028b14e35bdd670f59</t>
+  </si>
+  <si>
+    <t>c79f075871f2e21eb72d55919dc06e07</t>
   </si>
   <si>
     <t>c0a61e80cbdad1d36461054d8b76922b</t>
@@ -71,6 +71,87 @@
   </si>
   <si>
     <t>8c12df6869057b0cc7a986e5fd48e121</t>
+  </si>
+  <si>
+    <t>e8136e550290fc3ebc154f49253671db</t>
+  </si>
+  <si>
+    <t>b9083f0d038daab7cf4f7e51cb6c0427</t>
+  </si>
+  <si>
+    <t>0bd367cf924431ff69406e38f1633730</t>
+  </si>
+  <si>
+    <t>5f5ba28450a8f118b7a98d5d286129be</t>
+  </si>
+  <si>
+    <t>74a4be28b8ade27b84e7f0127bf55976</t>
+  </si>
+  <si>
+    <t>d32fd599f27709dc7f1f1b7c3e8f96e9</t>
+  </si>
+  <si>
+    <t>777adee7eabb01195a61568d3ed3d4e0</t>
+  </si>
+  <si>
+    <t>5f75801665b9c7dc39199b38908978b2</t>
+  </si>
+  <si>
+    <t>a921e0a7078b2253154d140e9b79cdf3</t>
+  </si>
+  <si>
+    <t>280ad677a381ff87522305766ec00e4c</t>
+  </si>
+  <si>
+    <t>74561771fdbb35087a7210735ed2db5c</t>
+  </si>
+  <si>
+    <t>a21f9b657bf9304a79cdeb38b84ecfa3</t>
+  </si>
+  <si>
+    <t>ed7e4b0108331d0bb4848a72433ae15c</t>
+  </si>
+  <si>
+    <t>dc165ce2bbee0646ab6cdf54d2a37642</t>
+  </si>
+  <si>
+    <t>fa5cfa29e1c7a6afd857d9f22c4fb4e7</t>
+  </si>
+  <si>
+    <t>ec749f910c94973b3902596eda728c3b</t>
+  </si>
+  <si>
+    <t>991889eba4e7f850e6a2d1afa3c58b2a</t>
+  </si>
+  <si>
+    <t>9f04f1828f7d431686c8cbc43bb2e5e2</t>
+  </si>
+  <si>
+    <t>4728279deb0d7642d8675627177a083b</t>
+  </si>
+  <si>
+    <t>4b41ee1498bc45df728c12f23cfb727b</t>
+  </si>
+  <si>
+    <t>cd2ab06c6e8a5f6c462df81187f94e43</t>
+  </si>
+  <si>
+    <t>c21eb1614f9b0a0d81a366f4882ea898</t>
+  </si>
+  <si>
+    <t>dfcc5b3d9f7c97ac3da1f0b01202fbb4</t>
+  </si>
+  <si>
+    <t>3895784bd78b266b14b9400dd3ef7551</t>
+  </si>
+  <si>
+    <t>0f85d25cfe48cf80c50fd7cc90d4a9f7</t>
+  </si>
+  <si>
+    <t>5cca3ad605c375d5f6daa71bddd93578</t>
+  </si>
+  <si>
+    <t>64b3ef0d858e3055a7b5f46526e6b7d5</t>
   </si>
 </sst>
 </file>
@@ -431,6 +512,141 @@
         <v>19</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/api-keys.xlsx
+++ b/api-keys.xlsx
@@ -11,18 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>b05449c580f85012517bb646171428a5</t>
-  </si>
-  <si>
-    <t>5ebaca909569476602d593ea0cd79680</t>
-  </si>
-  <si>
-    <t>e98b3aed4a763d704339d3c148ee6c3e</t>
-  </si>
-  <si>
-    <t>19ea79044fa1ac37de2e28f55eaa7ed2</t>
   </si>
   <si>
     <t>a5c889290ed179028b14e35bdd670f59</t>
@@ -632,21 +623,6 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
